--- a/Models/Молоко/Датасет по молоку wide.xlsx
+++ b/Models/Молоко/Датасет по молоку wide.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U121"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7877,6 +7877,475 @@
         <v>28616.8</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>11378.1</v>
+      </c>
+      <c r="C122" t="n">
+        <v>3645.1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>18568.9</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1102.6</v>
+      </c>
+      <c r="F122" t="n">
+        <v>11925.9</v>
+      </c>
+      <c r="G122" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="H122" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I122" t="n">
+        <v>4112</v>
+      </c>
+      <c r="J122" t="n">
+        <v>11870.5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3211.2</v>
+      </c>
+      <c r="L122" t="n">
+        <v>4413.5</v>
+      </c>
+      <c r="M122" t="n">
+        <v>12296.7</v>
+      </c>
+      <c r="N122" t="n">
+        <v>3000.2</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>9509.799999999999</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>10947.2</v>
+      </c>
+      <c r="R122" t="n">
+        <v>943.5999999999999</v>
+      </c>
+      <c r="S122" t="n">
+        <v>15361.5</v>
+      </c>
+      <c r="T122" t="n">
+        <v>17844.5</v>
+      </c>
+      <c r="U122" t="n">
+        <v>33158</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>12075.2</v>
+      </c>
+      <c r="C123" t="n">
+        <v>7802.9</v>
+      </c>
+      <c r="D123" t="n">
+        <v>16396.4</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1147.4</v>
+      </c>
+      <c r="F123" t="n">
+        <v>13309</v>
+      </c>
+      <c r="G123" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="H123" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I123" t="n">
+        <v>4463.5</v>
+      </c>
+      <c r="J123" t="n">
+        <v>11950.3</v>
+      </c>
+      <c r="K123" t="n">
+        <v>6609.1</v>
+      </c>
+      <c r="L123" t="n">
+        <v>7045.2</v>
+      </c>
+      <c r="M123" t="n">
+        <v>14608.5</v>
+      </c>
+      <c r="N123" t="n">
+        <v>3036.2</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>12638.2</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>9818</v>
+      </c>
+      <c r="R123" t="n">
+        <v>2536.8</v>
+      </c>
+      <c r="S123" t="n">
+        <v>15701.3</v>
+      </c>
+      <c r="T123" t="n">
+        <v>18781.6</v>
+      </c>
+      <c r="U123" t="n">
+        <v>35623.7</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>18113.7</v>
+      </c>
+      <c r="C124" t="n">
+        <v>14584.2</v>
+      </c>
+      <c r="D124" t="n">
+        <v>20150.5</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1787.2</v>
+      </c>
+      <c r="F124" t="n">
+        <v>17781.5</v>
+      </c>
+      <c r="G124" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I124" t="n">
+        <v>5183.200000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>12804.8</v>
+      </c>
+      <c r="K124" t="n">
+        <v>9067.299999999999</v>
+      </c>
+      <c r="L124" t="n">
+        <v>16438.5</v>
+      </c>
+      <c r="M124" t="n">
+        <v>15571.1</v>
+      </c>
+      <c r="N124" t="n">
+        <v>3195.7</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>20932.4</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>16812.4</v>
+      </c>
+      <c r="R124" t="n">
+        <v>4311.9</v>
+      </c>
+      <c r="S124" t="n">
+        <v>19059</v>
+      </c>
+      <c r="T124" t="n">
+        <v>22952.8</v>
+      </c>
+      <c r="U124" t="n">
+        <v>44086.4</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>20536.1</v>
+      </c>
+      <c r="C125" t="n">
+        <v>12551</v>
+      </c>
+      <c r="D125" t="n">
+        <v>19816.5</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2839.9</v>
+      </c>
+      <c r="F125" t="n">
+        <v>21818.7</v>
+      </c>
+      <c r="G125" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H125" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I125" t="n">
+        <v>6926.200000000001</v>
+      </c>
+      <c r="J125" t="n">
+        <v>20325.3</v>
+      </c>
+      <c r="K125" t="n">
+        <v>19342.5</v>
+      </c>
+      <c r="L125" t="n">
+        <v>16593.3</v>
+      </c>
+      <c r="M125" t="n">
+        <v>25665.2</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3601.1</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>26104.5</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>19826.1</v>
+      </c>
+      <c r="R125" t="n">
+        <v>5524.8</v>
+      </c>
+      <c r="S125" t="n">
+        <v>21595.3</v>
+      </c>
+      <c r="T125" t="n">
+        <v>34340.3</v>
+      </c>
+      <c r="U125" t="n">
+        <v>49990.5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>24905.7</v>
+      </c>
+      <c r="C126" t="n">
+        <v>15396.2</v>
+      </c>
+      <c r="D126" t="n">
+        <v>23213</v>
+      </c>
+      <c r="E126" t="n">
+        <v>5432.7</v>
+      </c>
+      <c r="F126" t="n">
+        <v>24180</v>
+      </c>
+      <c r="G126" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="H126" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I126" t="n">
+        <v>7755.3</v>
+      </c>
+      <c r="J126" t="n">
+        <v>21966.6</v>
+      </c>
+      <c r="K126" t="n">
+        <v>35421.8</v>
+      </c>
+      <c r="L126" t="n">
+        <v>25008.4</v>
+      </c>
+      <c r="M126" t="n">
+        <v>24862.8</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3887.4</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>30026.3</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>19147.2</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7606.299999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>23858.2</v>
+      </c>
+      <c r="T126" t="n">
+        <v>38714.8</v>
+      </c>
+      <c r="U126" t="n">
+        <v>59303.1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>28491.6</v>
+      </c>
+      <c r="C127" t="n">
+        <v>26838.1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>33260.5</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4032.2</v>
+      </c>
+      <c r="F127" t="n">
+        <v>30155.4</v>
+      </c>
+      <c r="G127" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H127" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I127" t="n">
+        <v>8152.1</v>
+      </c>
+      <c r="J127" t="n">
+        <v>29428.1</v>
+      </c>
+      <c r="K127" t="n">
+        <v>40245.9</v>
+      </c>
+      <c r="L127" t="n">
+        <v>33051.3</v>
+      </c>
+      <c r="M127" t="n">
+        <v>48355.4</v>
+      </c>
+      <c r="N127" t="n">
+        <v>4754.3</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>43388.8</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>27639</v>
+      </c>
+      <c r="R127" t="n">
+        <v>5966.7</v>
+      </c>
+      <c r="S127" t="n">
+        <v>29471.7</v>
+      </c>
+      <c r="T127" t="n">
+        <v>45201.5</v>
+      </c>
+      <c r="U127" t="n">
+        <v>61702.9</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>25379.9</v>
+      </c>
+      <c r="C128" t="n">
+        <v>22505.1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>31438.9</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2987.3</v>
+      </c>
+      <c r="F128" t="n">
+        <v>28246.7</v>
+      </c>
+      <c r="G128" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I128" t="n">
+        <v>6931.2</v>
+      </c>
+      <c r="J128" t="n">
+        <v>22638.4</v>
+      </c>
+      <c r="K128" t="n">
+        <v>28134.5</v>
+      </c>
+      <c r="L128" t="n">
+        <v>22114.3</v>
+      </c>
+      <c r="M128" t="n">
+        <v>24434.4</v>
+      </c>
+      <c r="N128" t="n">
+        <v>4682.9</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>37435.4</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>21703.2</v>
+      </c>
+      <c r="R128" t="n">
+        <v>10042.5</v>
+      </c>
+      <c r="S128" t="n">
+        <v>28373.2</v>
+      </c>
+      <c r="T128" t="n">
+        <v>46680.7</v>
+      </c>
+      <c r="U128" t="n">
+        <v>43495.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
